--- a/data/modelamiento/comparacion_escenarios_modelamiento.xlsx
+++ b/data/modelamiento/comparacion_escenarios_modelamiento.xlsx
@@ -1213,7 +1213,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3484,9 +3484,6 @@
       <c r="J9">
         <v>-0.061524</v>
       </c>
-      <c r="K9">
-        <v>-1</v>
-      </c>
       <c r="L9">
         <v>0</v>
       </c>
@@ -4286,9 +4283,6 @@
       <c r="J23">
         <v>-0.173611</v>
       </c>
-      <c r="K23">
-        <v>-1</v>
-      </c>
       <c r="L23">
         <v>0</v>
       </c>
@@ -5088,9 +5082,6 @@
       <c r="J37">
         <v>-0.0396</v>
       </c>
-      <c r="K37">
-        <v>-1</v>
-      </c>
       <c r="L37">
         <v>0</v>
       </c>
@@ -5890,9 +5881,6 @@
       <c r="J51">
         <v>-0.173611</v>
       </c>
-      <c r="K51">
-        <v>-1</v>
-      </c>
       <c r="L51">
         <v>0</v>
       </c>
@@ -6692,9 +6680,6 @@
       <c r="J65">
         <v>-0.028123</v>
       </c>
-      <c r="K65">
-        <v>-0.501933</v>
-      </c>
       <c r="L65">
         <v>-0.001746</v>
       </c>
@@ -7494,9 +7479,6 @@
       <c r="J79">
         <v>-0.027447</v>
       </c>
-      <c r="K79">
-        <v>-0.407763</v>
-      </c>
       <c r="L79">
         <v>-0.000175</v>
       </c>
@@ -8295,9 +8277,6 @@
       </c>
       <c r="J93">
         <v>-0.049375</v>
-      </c>
-      <c r="K93">
-        <v>-1</v>
       </c>
       <c r="L93">
         <v>-0</v>
@@ -14396,9 +14375,6 @@
       <c r="F3">
         <v>-0.061524</v>
       </c>
-      <c r="G3">
-        <v>-1</v>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>random_forest_restringido</t>
@@ -14532,9 +14508,6 @@
       <c r="F5">
         <v>-0.173611</v>
       </c>
-      <c r="G5">
-        <v>-1</v>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>random_forest_restringido</t>
@@ -14668,9 +14641,6 @@
       <c r="F7">
         <v>-0.0396</v>
       </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>random_forest_restringido</t>
@@ -14804,9 +14774,6 @@
       <c r="F9">
         <v>-0.173611</v>
       </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>random_forest_restringido</t>
@@ -14940,9 +14907,6 @@
       <c r="F11">
         <v>-0.028123</v>
       </c>
-      <c r="G11">
-        <v>-0.501933</v>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>random_forest_restringido</t>
@@ -15076,9 +15040,6 @@
       <c r="F13">
         <v>-0.027447</v>
       </c>
-      <c r="G13">
-        <v>-0.407763</v>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>gradient_boosting_restringido</t>
@@ -15211,9 +15172,6 @@
       </c>
       <c r="F15">
         <v>-0.049375</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -15534,7 +15492,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -15615,25 +15573,35 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>importancia_norm_minmax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>score_combinado</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>estabilidad_consenso</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>prioridad_tesis</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ranking_consenso</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>orden_escenario</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>lectura_final</t>
         </is>
@@ -15652,12 +15620,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>x_gcfid_guaiacol_ppm</t>
+          <t>x_gcfid_4_ethyl_guaiacol_ppm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gcfid guaiacol ppm</t>
+          <t>gcfid 4 ethyl guaiacol ppm</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15684,42 +15652,48 @@
         </is>
       </c>
       <c r="J2">
-        <v>0.9225</v>
+        <v>0.7275</v>
       </c>
       <c r="K2">
         <v>0.99</v>
       </c>
       <c r="L2">
-        <v>17.53402248779114</v>
+        <v>37.00629480951667</v>
       </c>
       <c r="M2">
-        <v>32.32363828864813</v>
+        <v>55.05258287798129</v>
       </c>
       <c r="N2">
-        <v>369</v>
+        <v>291</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>0.86375</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R2">
+      <c r="T2">
         <v>1</v>
       </c>
-      <c r="S2">
+      <c r="U2">
         <v>1</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>variable_prioritaria_directa</t>
         </is>
@@ -15738,12 +15712,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>x_gcfid_p_cresol_ppm</t>
+          <t>x_gcfid_o_cresol_ppm</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>gcfid p cresol ppm</t>
+          <t>gcfid o cresol ppm</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15770,42 +15744,48 @@
         </is>
       </c>
       <c r="J3">
-        <v>0.845</v>
+        <v>0.775</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>15.64268494518121</v>
+        <v>24.7345254209672</v>
       </c>
       <c r="M3">
-        <v>20.46041263495372</v>
+        <v>42.04518748284477</v>
       </c>
       <c r="N3">
-        <v>338</v>
+        <v>310</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3">
+        <v>0.649892437001329</v>
+      </c>
+      <c r="Q3">
+        <v>0.7124462185006646</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>2</v>
       </c>
-      <c r="S3">
+      <c r="U3">
         <v>1</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>variable_prioritaria_directa</t>
         </is>
@@ -15824,12 +15804,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>x_gcfid_o_cresol_ppm</t>
+          <t>x_gcfid_guaiacol_ppm</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>gcfid o cresol ppm</t>
+          <t>gcfid guaiacol ppm</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15856,42 +15836,48 @@
         </is>
       </c>
       <c r="J4">
-        <v>0.775</v>
+        <v>0.9225</v>
       </c>
       <c r="K4">
+        <v>0.99</v>
+      </c>
+      <c r="L4">
+        <v>17.53402248779114</v>
+      </c>
+      <c r="M4">
+        <v>32.32363828864813</v>
+      </c>
+      <c r="N4">
+        <v>369</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
+        </is>
+      </c>
+      <c r="P4">
+        <v>0.4444656191985679</v>
+      </c>
+      <c r="Q4">
+        <v>0.683482809599284</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>prioritaria</t>
+        </is>
+      </c>
+      <c r="T4">
+        <v>3</v>
+      </c>
+      <c r="U4">
         <v>1</v>
       </c>
-      <c r="L4">
-        <v>24.7345254209672</v>
-      </c>
-      <c r="M4">
-        <v>42.04518748284477</v>
-      </c>
-      <c r="N4">
-        <v>310</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>prioritaria</t>
-        </is>
-      </c>
-      <c r="R4">
-        <v>3</v>
-      </c>
-      <c r="S4">
-        <v>1</v>
-      </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>variable_prioritaria_directa</t>
         </is>
@@ -15910,12 +15896,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_octanoate_ppm</t>
+          <t>x_gcfid_p_cresol_ppm</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>gcfid ethyl octanoate ppm</t>
+          <t>gcfid p cresol ppm</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15925,12 +15911,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>media_contextual</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H5">
@@ -15942,44 +15928,50 @@
         </is>
       </c>
       <c r="J5">
-        <v>0.7375</v>
+        <v>0.845</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5">
-        <v>2.319313847251581</v>
+        <v>15.64268494518121</v>
       </c>
       <c r="M5">
-        <v>9.17233425056237</v>
+        <v>20.46041263495372</v>
       </c>
       <c r="N5">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
+        </is>
+      </c>
+      <c r="P5">
+        <v>0.3905066865552512</v>
+      </c>
+      <c r="Q5">
+        <v>0.6177533432776255</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R5">
+      <c r="T5">
         <v>4</v>
       </c>
-      <c r="S5">
+      <c r="U5">
         <v>1</v>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>variable_prioritaria_indirecta</t>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>variable_prioritaria_directa</t>
         </is>
       </c>
     </row>
@@ -15996,27 +15988,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>x_gcfid_4_ethyl_guaiacol_ppm</t>
+          <t>x_gcms_area_valida_pct</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>gcfid 4 ethyl guaiacol ppm</t>
+          <t>gcms area valida pct</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>GC-MS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>calidad_senal_analitica</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>baja_contextual</t>
         </is>
       </c>
       <c r="H6">
@@ -16028,44 +16020,50 @@
         </is>
       </c>
       <c r="J6">
-        <v>0.7275</v>
+        <v>0.7775</v>
       </c>
       <c r="K6">
-        <v>0.99</v>
+        <v>0.86</v>
       </c>
       <c r="L6">
-        <v>37.00629480951667</v>
+        <v>4.919758192966127</v>
       </c>
       <c r="M6">
-        <v>55.05258287798129</v>
+        <v>10.93504676509307</v>
       </c>
       <c r="N6">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P6">
+        <v>0.0845868444716619</v>
+      </c>
+      <c r="Q6">
+        <v>0.4310434222358309</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>prioritaria</t>
-        </is>
-      </c>
-      <c r="R6">
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>apoyo_interpretativo</t>
+        </is>
+      </c>
+      <c r="T6">
         <v>5</v>
       </c>
-      <c r="S6">
+      <c r="U6">
         <v>1</v>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>variable_prioritaria_directa</t>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
     </row>
@@ -16082,12 +16080,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>x_gcms_area_valida_pct</t>
+          <t>x_gcms_aldehidos_pct</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>gcms area valida pct</t>
+          <t>gcms aldehidos pct</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -16097,7 +16095,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>calidad_senal_analitica</t>
+          <t>aldehidos_furanicos</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -16114,42 +16112,48 @@
         </is>
       </c>
       <c r="J7">
-        <v>0.7775</v>
+        <v>0.6375</v>
       </c>
       <c r="K7">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="L7">
-        <v>4.919758192966127</v>
+        <v>7.549019384440903</v>
       </c>
       <c r="M7">
-        <v>10.93504676509307</v>
+        <v>12.78118167873715</v>
       </c>
       <c r="N7">
-        <v>311</v>
+        <v>255</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="P7">
+        <v>0.1595983769645344</v>
+      </c>
+      <c r="Q7">
+        <v>0.3985491884822672</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R7">
+      <c r="T7">
         <v>6</v>
       </c>
-      <c r="S7">
+      <c r="U7">
         <v>1</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
@@ -16168,12 +16172,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>x_gcfid_ethyl_hexadecanoate_ppm</t>
+          <t>x_gcfid_ethyl_octanoate_ppm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>gcfid ethyl hexadecanoate ppm</t>
+          <t>gcfid ethyl octanoate ppm</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -16200,42 +16204,48 @@
         </is>
       </c>
       <c r="J8">
-        <v>0.6575</v>
+        <v>0.7375</v>
       </c>
       <c r="K8">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>3.386988003710015</v>
+        <v>2.319313847251581</v>
       </c>
       <c r="M8">
-        <v>13.03106524617043</v>
+        <v>9.17233425056237</v>
       </c>
       <c r="N8">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="P8">
+        <v>0.01039744245753168</v>
+      </c>
+      <c r="Q8">
+        <v>0.3739487212287659</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R8">
+      <c r="T8">
         <v>7</v>
       </c>
-      <c r="S8">
+      <c r="U8">
         <v>1</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
@@ -16254,27 +16264,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>x_gcms_fenolicos_pct</t>
+          <t>x_gcfid_isoamyl_acetate_ppm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>gcms fenolicos pct</t>
+          <t>gcfid isoamyl acetate ppm</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GC-MS</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>media_contextual</t>
         </is>
       </c>
       <c r="H9">
@@ -16286,42 +16296,48 @@
         </is>
       </c>
       <c r="J9">
-        <v>0.655</v>
+        <v>0.6475</v>
       </c>
       <c r="K9">
         <v>0.87</v>
       </c>
       <c r="L9">
-        <v>4.16328339683232</v>
+        <v>5.046468962427659</v>
       </c>
       <c r="M9">
-        <v>6.660799562739052</v>
+        <v>13.5782129420379</v>
       </c>
       <c r="N9">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
+          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P9">
+        <v>0.08820184058976505</v>
+      </c>
+      <c r="Q9">
+        <v>0.3678509202948825</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R9">
+      <c r="T9">
         <v>8</v>
       </c>
-      <c r="S9">
+      <c r="U9">
         <v>1</v>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
@@ -16340,12 +16356,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>x_gcfid_isoamyl_acetate_ppm</t>
+          <t>x_gcfid_furfural_ppm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>gcfid isoamyl acetate ppm</t>
+          <t>gcfid furfural ppm</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -16355,12 +16371,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>esteres</t>
+          <t>aldehidos_furanicos</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>media_contextual</t>
+          <t>baja_contextual</t>
         </is>
       </c>
       <c r="H10">
@@ -16372,42 +16388,48 @@
         </is>
       </c>
       <c r="J10">
-        <v>0.6475</v>
+        <v>0.6325</v>
       </c>
       <c r="K10">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L10">
-        <v>5.046468962427659</v>
+        <v>5.22821072853028</v>
       </c>
       <c r="M10">
-        <v>13.5782129420379</v>
+        <v>12.35358468855084</v>
       </c>
       <c r="N10">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
+        </is>
+      </c>
+      <c r="P10">
+        <v>0.09338684405671695</v>
+      </c>
+      <c r="Q10">
+        <v>0.3629434220283584</v>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R10">
+      <c r="T10">
         <v>9</v>
       </c>
-      <c r="S10">
+      <c r="U10">
         <v>1</v>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
@@ -16426,12 +16448,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>x_gcms_aldehidos_pct</t>
+          <t>x_gcms_fenolicos_pct</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>gcms aldehidos pct</t>
+          <t>gcms fenolicos pct</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16441,12 +16463,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>aldehidos_furanicos</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>baja_contextual</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H11">
@@ -16458,42 +16480,48 @@
         </is>
       </c>
       <c r="J11">
-        <v>0.6375</v>
+        <v>0.655</v>
       </c>
       <c r="K11">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="L11">
-        <v>7.549019384440903</v>
+        <v>4.16328339683232</v>
       </c>
       <c r="M11">
-        <v>12.78118167873715</v>
+        <v>6.660799562739052</v>
       </c>
       <c r="N11">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
+        </is>
+      </c>
+      <c r="P11">
+        <v>0.06300498948737189</v>
+      </c>
+      <c r="Q11">
+        <v>0.359002494743686</v>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R11">
+      <c r="T11">
         <v>10</v>
       </c>
-      <c r="S11">
+      <c r="U11">
         <v>1</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
@@ -16512,12 +16540,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>x_gcfid_furfural_ppm</t>
+          <t>x_gcfid_ethyl_hexadecanoate_ppm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>gcfid furfural ppm</t>
+          <t>gcfid ethyl hexadecanoate ppm</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16527,12 +16555,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>aldehidos_furanicos</t>
+          <t>esteres</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>baja_contextual</t>
+          <t>media_contextual</t>
         </is>
       </c>
       <c r="H12">
@@ -16544,42 +16572,48 @@
         </is>
       </c>
       <c r="J12">
-        <v>0.6325</v>
+        <v>0.6575</v>
       </c>
       <c r="K12">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="L12">
-        <v>5.22821072853028</v>
+        <v>3.386988003710015</v>
       </c>
       <c r="M12">
-        <v>12.35358468855084</v>
+        <v>13.03106524617043</v>
       </c>
       <c r="N12">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
+          <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P12">
+        <v>0.04085766259034398</v>
+      </c>
+      <c r="Q12">
+        <v>0.349178831295172</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R12">
+      <c r="T12">
         <v>11</v>
       </c>
-      <c r="S12">
+      <c r="U12">
         <v>1</v>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
@@ -16649,23 +16683,29 @@
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13">
+        <v>0.0001236281148683102</v>
+      </c>
+      <c r="Q13">
+        <v>0.2950618140574341</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R13">
+      <c r="T13">
         <v>12</v>
       </c>
-      <c r="S13">
+      <c r="U13">
         <v>1</v>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
@@ -16735,23 +16775,29 @@
           <t>Interpretacion contextual: los esteres pueden separar perfiles de muestra, pero no son evidencia fenolica directa.</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14">
+        <v>0.02844236402745124</v>
+      </c>
+      <c r="Q14">
+        <v>0.2917211820137256</v>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R14">
+      <c r="T14">
         <v>13</v>
       </c>
-      <c r="S14">
+      <c r="U14">
         <v>1</v>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
@@ -16821,23 +16867,29 @@
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0.2775</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R15">
+      <c r="T15">
         <v>14</v>
       </c>
-      <c r="S15">
+      <c r="U15">
         <v>1</v>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
@@ -16856,27 +16908,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>x_ju_maltose_consumption_g_l</t>
+          <t>x_gcfid_4_ethyl_guaiacol_ppm</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ju maltose consumption g l</t>
+          <t>gcfid 4 ethyl guaiacol ppm</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JU</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>fermentacion_indirecta</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>media_indirecta</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H16">
@@ -16888,44 +16940,50 @@
         </is>
       </c>
       <c r="J16">
-        <v>0.9025000000000001</v>
+        <v>0.825</v>
       </c>
       <c r="K16">
+        <v>0.95</v>
+      </c>
+      <c r="L16">
+        <v>36.21920442171134</v>
+      </c>
+      <c r="M16">
+        <v>51.89013760839237</v>
+      </c>
+      <c r="N16">
+        <v>330</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
+        </is>
+      </c>
+      <c r="P16">
         <v>1</v>
       </c>
-      <c r="L16">
-        <v>8.006378279693029</v>
-      </c>
-      <c r="M16">
-        <v>30.13008720070722</v>
-      </c>
-      <c r="N16">
-        <v>361</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16">
+        <v>0.9125</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R16">
+      <c r="T16">
         <v>1</v>
       </c>
-      <c r="S16">
+      <c r="U16">
         <v>2</v>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>variable_prioritaria_indirecta</t>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>variable_prioritaria_directa</t>
         </is>
       </c>
     </row>
@@ -16993,23 +17051,29 @@
           <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17">
+        <v>0.8354031360649414</v>
+      </c>
+      <c r="Q17">
+        <v>0.8677015680324707</v>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>prioritaria</t>
         </is>
       </c>
-      <c r="R17">
+      <c r="T17">
         <v>2</v>
       </c>
-      <c r="S17">
+      <c r="U17">
         <v>2</v>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>variable_prioritaria_directa</t>
         </is>
@@ -17028,27 +17092,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>x_gcfid_4_ethyl_guaiacol_ppm</t>
+          <t>x_ju_maltose_consumption_g_l</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>gcfid 4 ethyl guaiacol ppm</t>
+          <t>ju maltose consumption g l</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>JU</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>fermentacion_indirecta</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>media_indirecta</t>
         </is>
       </c>
       <c r="H18">
@@ -17060,44 +17124,50 @@
         </is>
       </c>
       <c r="J18">
-        <v>0.825</v>
+        <v>0.9025000000000001</v>
       </c>
       <c r="K18">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>36.21920442171134</v>
+        <v>8.006378279693029</v>
       </c>
       <c r="M18">
-        <v>51.89013760839237</v>
+        <v>30.13008720070722</v>
       </c>
       <c r="N18">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
+          <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P18">
+        <v>0.2174170554261122</v>
+      </c>
+      <c r="Q18">
+        <v>0.5599585277130561</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>prioritaria</t>
-        </is>
-      </c>
-      <c r="R18">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>apoyo_interpretativo</t>
+        </is>
+      </c>
+      <c r="T18">
         <v>3</v>
       </c>
-      <c r="S18">
+      <c r="U18">
         <v>2</v>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>variable_prioritaria_directa</t>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
     </row>
@@ -17165,25 +17235,31 @@
           <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19">
+        <v>0.2152059062818368</v>
+      </c>
+      <c r="Q19">
+        <v>0.4876029531409184</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>prioritaria</t>
-        </is>
-      </c>
-      <c r="R19">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>apoyo_interpretativo</t>
+        </is>
+      </c>
+      <c r="T19">
         <v>4</v>
       </c>
-      <c r="S19">
+      <c r="U19">
         <v>2</v>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>variable_prioritaria_indirecta</t>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
     </row>
@@ -17200,27 +17276,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>x_gcfid_guaiacol_ppm</t>
+          <t>x_ju_ethanol_production_g_l</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>gcfid guaiacol ppm</t>
+          <t>ju ethanol production g l</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GC-FID</t>
+          <t>JU</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>fenoles_volatiles</t>
+          <t>fermentacion_indirecta</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>alta_directa</t>
+          <t>media_indirecta</t>
         </is>
       </c>
       <c r="H20">
@@ -17232,44 +17308,50 @@
         </is>
       </c>
       <c r="J20">
-        <v>0.7524999999999999</v>
+        <v>0.6675</v>
       </c>
       <c r="K20">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="L20">
-        <v>3.178167395991517</v>
+        <v>7.855940633058448</v>
       </c>
       <c r="M20">
-        <v>4.341506335983394</v>
+        <v>27.99051361055944</v>
       </c>
       <c r="N20">
-        <v>301</v>
+        <v>267</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>prioritaria</t>
-        </is>
-      </c>
-      <c r="R20">
+          <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
+        </is>
+      </c>
+      <c r="P20">
+        <v>0.2132441329444925</v>
+      </c>
+      <c r="Q20">
+        <v>0.4403720664722462</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>apoyo_interpretativo</t>
+        </is>
+      </c>
+      <c r="T20">
         <v>5</v>
       </c>
-      <c r="S20">
+      <c r="U20">
         <v>2</v>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>variable_prioritaria_directa</t>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
     </row>
@@ -17286,27 +17368,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>x_ju_ethanol_production_g_l</t>
+          <t>x_gcfid_guaiacol_ppm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ju ethanol production g l</t>
+          <t>gcfid guaiacol ppm</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>JU</t>
+          <t>GC-FID</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>fermentacion_indirecta</t>
+          <t>fenoles_volatiles</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>media_indirecta</t>
+          <t>alta_directa</t>
         </is>
       </c>
       <c r="H21">
@@ -17318,42 +17400,48 @@
         </is>
       </c>
       <c r="J21">
-        <v>0.6675</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="K21">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="L21">
-        <v>7.855940633058448</v>
+        <v>3.178167395991517</v>
       </c>
       <c r="M21">
-        <v>27.99051361055944</v>
+        <v>4.341506335983394</v>
       </c>
       <c r="N21">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Interpretacion indirecta: puede capturar diferencias de fermentacion o bloque analitico, no causalidad fenolica directa.</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
+          <t>Coherente: cresoles, guaiacol u otros fenoles volatiles se relacionan directamente con notas fenolicas/ahumadas.</t>
+        </is>
+      </c>
+      <c r="P21">
+        <v>0.08348947683576985</v>
+      </c>
+      <c r="Q21">
+        <v>0.4179947384178849</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R21">
+      <c r="T21">
         <v>6</v>
       </c>
-      <c r="S21">
+      <c r="U21">
         <v>2</v>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
@@ -17423,23 +17511,29 @@
           <t>Debe interpretarse como asociacion estadistica exploratoria y contrastarse con literatura/criterio experto.</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22">
+        <v>0.0485117596914657</v>
+      </c>
+      <c r="Q22">
+        <v>0.3455058798457329</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
       </c>
-      <c r="R22">
+      <c r="T22">
         <v>7</v>
       </c>
-      <c r="S22">
+      <c r="U22">
         <v>2</v>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>apoyo_interpretativo</t>
         </is>
@@ -17540,7 +17634,7 @@
         <v>0.8374999999999999</v>
       </c>
       <c r="H2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -17586,7 +17680,7 @@
         <v>0.8374999999999999</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -17632,7 +17726,7 @@
         <v>0.77625</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -17678,7 +17772,7 @@
         <v>0.71</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -17724,11 +17818,11 @@
         <v>0.9025000000000001</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -17770,7 +17864,7 @@
         <v>0.845</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -17820,7 +17914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -17862,11 +17956,11 @@
         <v>0.7375</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>prioritaria</t>
+          <t>apoyo_interpretativo</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -17908,7 +18002,7 @@
         <v>0.6675</v>
       </c>
       <c r="H10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -17954,7 +18048,7 @@
         <v>0.6575</v>
       </c>
       <c r="H11">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -18000,7 +18094,7 @@
         <v>0.655</v>
       </c>
       <c r="H12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -18046,7 +18140,7 @@
         <v>0.6475</v>
       </c>
       <c r="H13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -18092,7 +18186,7 @@
         <v>0.6375</v>
       </c>
       <c r="H14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -18138,7 +18232,7 @@
         <v>0.6325</v>
       </c>
       <c r="H15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
